--- a/Impulsivity_data/MYT1L_Impulsivity_Key.xlsx
+++ b/Impulsivity_data/MYT1L_Impulsivity_Key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Murrell\OneDrive - Washington University in St. Louis\Documents\Github\MYT1L\Impulsivity_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09C0077-EAAC-442A-A6E5-CE540E54AED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FEC559-AEAD-4861-8369-740C756BF772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24465" yWindow="4065" windowWidth="23505" windowHeight="13050" xr2:uid="{485FC1DE-5247-4110-9F8E-CFCD702DA0AA}"/>
+    <workbookView xWindow="2535" yWindow="2400" windowWidth="25680" windowHeight="13050" xr2:uid="{485FC1DE-5247-4110-9F8E-CFCD702DA0AA}"/>
   </bookViews>
   <sheets>
     <sheet name="MYT1L_Impulsivity_Key" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
   <si>
     <t>Mouse_ID</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>FED3</t>
+  </si>
+  <si>
+    <t>3+57</t>
+  </si>
+  <si>
+    <t>FED_StartDate1</t>
   </si>
 </sst>
 </file>
@@ -143,9 +149,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,13 +487,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A334FCC-C21E-4F7B-B473-AD06E865A26A}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,10 +511,13 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -525,8 +536,11 @@
       <c r="F2" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -545,8 +559,11 @@
       <c r="F3" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -565,8 +582,11 @@
       <c r="F4" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -585,8 +605,11 @@
       <c r="F5" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -599,14 +622,17 @@
       <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E6">
-        <v>3</v>
+      <c r="E6" t="s">
+        <v>21</v>
       </c>
       <c r="F6" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -625,8 +651,11 @@
       <c r="F7" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -645,8 +674,11 @@
       <c r="F8" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -665,8 +697,11 @@
       <c r="F9" s="1">
         <v>46251</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="2">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -684,6 +719,9 @@
       </c>
       <c r="F10" s="1">
         <v>46251</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46289</v>
       </c>
     </row>
   </sheetData>
